--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8591" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8665" uniqueCount="1018">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DIPSPatient</t>
+    <t>http://dips.no/fhir/StructureDefinition/R4/DIPSPatient</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:16:58+00:00</t>
+    <t>2026-09-08T11:30:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -912,7 +912,7 @@
     <t>deathRegisteredTime</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientDeathRegisteredTime}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientDeathRegisteredTime}
 </t>
   </si>
   <si>
@@ -928,7 +928,7 @@
     <t>deathComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientDeathComment}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientDeathComment}
 </t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>isUpdatedByPopulationRegister</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/IsUpdatedByPopulationRegister}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/IsUpdatedByPopulationRegister}
 </t>
   </si>
   <si>
@@ -948,7 +948,7 @@
     <t>deathRegisteredBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientDeathRegisteredBy}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DeathRegisteredBy}
 </t>
   </si>
   <si>
@@ -958,7 +958,7 @@
     <t>hospitalSectorId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientHospitalSectorId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientHospitalSectorId}
 </t>
   </si>
   <si>
@@ -968,7 +968,7 @@
     <t>hospitalSectorName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientHospitalSectorName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientHospitalSectorName}
 </t>
   </si>
   <si>
@@ -1810,8 +1810,40 @@
     <t>DipsPatientPhoneTypeId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientPhoneTypeId}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientPhoneTypeId}
 </t>
+  </si>
+  <si>
+    <t>Patient.telecom.extension:canReceiveSms</t>
+  </si>
+  <si>
+    <t>canReceiveSms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSCanReceiveSms}
+</t>
+  </si>
+  <si>
+    <t>DIPS Can Receive SMS</t>
+  </si>
+  <si>
+    <t>Indicates whether this phone number can receive SMS messages.</t>
+  </si>
+  <si>
+    <t>Patient.telecom.extension:commentText</t>
+  </si>
+  <si>
+    <t>commentText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSCommentText}
+</t>
+  </si>
+  <si>
+    <t>DIPS Comment Text</t>
+  </si>
+  <si>
+    <t>A free-text comment associated with this phone number.</t>
   </si>
   <si>
     <t>Patient.telecom.system</t>
@@ -2096,7 +2128,7 @@
     <t>StateName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientStateName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientStateName}
 </t>
   </si>
   <si>
@@ -2106,7 +2138,7 @@
     <t>LastOfficialAddressSyncTime</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/LastOfficialAddressSyncTime}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/LastOfficialAddressSyncTime}
 </t>
   </si>
   <si>
@@ -2295,7 +2327,7 @@
     <t>municipality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientMunicipality}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientMunicipality}
 </t>
   </si>
   <si>
@@ -2577,7 +2609,7 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPatientContactIdentifier}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientContactIdentifier}
 </t>
   </si>
   <si>
@@ -2587,7 +2619,7 @@
     <t>contactPratitionerRoleName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DIPSPatientContactPractitionerRoleName}
+    <t xml:space="preserve">Extension {http://dips.no/fhir/StructureDefinition/R4/DIPSPatientContactPractitionerRoleName}
 </t>
   </si>
   <si>
@@ -2755,7 +2787,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1) {http://dips.no/fhir/R4/StructureDefinition/DIPSOrganizationReference}
+    <t xml:space="preserve">Reference(Organization|4.0.1) {http://dips.no/fhir/StructureDefinition/R4/DIPSOrganizationReference}
 </t>
   </si>
   <si>
@@ -2877,7 +2909,7 @@
     <t>LanguageId</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://dips.no/fhir/R4/StructureDefinition/DipsPatientLanguageId}
+    <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/dips-patient-language-id}
 </t>
   </si>
   <si>
@@ -2905,7 +2937,7 @@
     <t>Patient.communication.language.coding.extension.url</t>
   </si>
   <si>
-    <t>http://dips.no/fhir/R4/StructureDefinition/DipsPatientLanguageId</t>
+    <t>http://hl7.no/fhir/StructureDefinition/dips-patient-language-id</t>
   </si>
   <si>
     <t>Patient.communication.language.coding:DipsCoding.extension:LanguageId.value[x]</t>
@@ -3034,7 +3066,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole|http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner|http://hl7.no/fhir/StructureDefinition/no-basis-PractitionerRole|http://hl7.no/fhir/StructureDefinition/no-basis-Organization) {http://dips.no/fhir/R4/StructureDefinition/DIPSPractitionerRoleReference}
+    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole|http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner|http://hl7.no/fhir/StructureDefinition/no-basis-PractitionerRole|http://hl7.no/fhir/StructureDefinition/no-basis-Organization) {http://dips.no/fhir/StructureDefinition/R4/DIPSPractitionerRoleReference}
 </t>
   </si>
   <si>
@@ -3058,7 +3090,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|http://hl7.no/fhir/StructureDefinition/no-basis-Organization) {http://dips.no/fhir/R4/StructureDefinition/DIPSOrganizationReference}
+    <t xml:space="preserve">Reference(Organization|http://hl7.no/fhir/StructureDefinition/no-basis-Organization) {http://dips.no/fhir/StructureDefinition/R4/DIPSOrganizationReference}
 </t>
   </si>
   <si>
@@ -3435,7 +3467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO231"/>
+  <dimension ref="A1:AO233"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.31640625" customWidth="true" bestFit="true"/>
@@ -18469,9 +18501,11 @@
         <v>582</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="D129" t="s" s="2">
         <v>79</v>
       </c>
@@ -18489,16 +18523,16 @@
         <v>79</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>175</v>
+        <v>584</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18525,13 +18559,13 @@
         <v>79</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>585</v>
+        <v>79</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>586</v>
+        <v>79</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>79</v>
@@ -18549,22 +18583,22 @@
         <v>79</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>587</v>
+        <v>115</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>588</v>
+        <v>79</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>589</v>
+        <v>79</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>79</v>
@@ -18573,7 +18607,7 @@
         <v>79</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>590</v>
+        <v>79</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>79</v>
@@ -18581,12 +18615,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>79</v>
       </c>
@@ -18604,23 +18640,19 @@
         <v>79</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>101</v>
+        <v>589</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>79</v>
       </c>
@@ -18668,22 +18700,22 @@
         <v>79</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>596</v>
+        <v>115</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>597</v>
+        <v>79</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>79</v>
@@ -18692,7 +18724,7 @@
         <v>79</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>598</v>
+        <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>79</v>
@@ -18700,10 +18732,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18720,7 +18752,7 @@
         <v>79</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>88</v>
@@ -18729,17 +18761,13 @@
         <v>175</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>79</v>
       </c>
@@ -18766,10 +18794,10 @@
         <v>328</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>79</v>
@@ -18787,7 +18815,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -18796,13 +18824,13 @@
         <v>87</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>79</v>
+        <v>598</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>523</v>
+        <v>599</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>79</v>
@@ -18811,7 +18839,7 @@
         <v>79</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18819,10 +18847,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18845,18 +18873,20 @@
         <v>88</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>609</v>
+        <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
       </c>
@@ -18904,7 +18934,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -18919,7 +18949,7 @@
         <v>99</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>105</v>
+        <v>607</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>79</v>
@@ -18928,7 +18958,7 @@
         <v>79</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18936,10 +18966,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18956,22 +18986,26 @@
         <v>79</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J133" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
       </c>
@@ -18995,13 +19029,13 @@
         <v>79</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>79</v>
+        <v>614</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>79</v>
+        <v>615</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>79</v>
@@ -19019,7 +19053,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -19034,7 +19068,7 @@
         <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>566</v>
+        <v>523</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>79</v>
@@ -19043,7 +19077,7 @@
         <v>79</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>236</v>
+        <v>617</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -19077,20 +19111,18 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>175</v>
+        <v>619</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O134" t="s" s="2">
         <v>622</v>
       </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>79</v>
       </c>
@@ -19114,31 +19146,31 @@
         <v>79</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF134" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -19153,16 +19185,16 @@
         <v>99</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>625</v>
+        <v>105</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>626</v>
+        <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>627</v>
+        <v>105</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19170,10 +19202,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19196,20 +19228,16 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>629</v>
+        <v>280</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>79</v>
       </c>
@@ -19257,7 +19285,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -19272,27 +19300,27 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>634</v>
+        <v>566</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>635</v>
+        <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>636</v>
+        <v>236</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>637</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19309,25 +19337,25 @@
         <v>79</v>
       </c>
       <c r="I136" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J136" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>639</v>
+        <v>175</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19352,13 +19380,13 @@
         <v>79</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>79</v>
+        <v>633</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>79</v>
+        <v>634</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>79</v>
@@ -19376,7 +19404,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -19391,16 +19419,16 @@
         <v>99</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>105</v>
+        <v>636</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19408,10 +19436,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19422,7 +19450,7 @@
         <v>77</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>79</v>
@@ -19434,19 +19462,19 @@
         <v>88</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19495,13 +19523,13 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>79</v>
@@ -19510,27 +19538,27 @@
         <v>99</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>79</v>
+        <v>647</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19547,22 +19575,26 @@
         <v>79</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>101</v>
+        <v>649</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>102</v>
+        <v>650</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>79</v>
       </c>
@@ -19610,7 +19642,7 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>104</v>
+        <v>648</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
@@ -19622,19 +19654,19 @@
         <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AL138" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AL138" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM138" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>79</v>
+        <v>655</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>79</v>
@@ -19665,19 +19697,23 @@
         <v>79</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>108</v>
+        <v>657</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>238</v>
+        <v>658</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
       </c>
@@ -19713,19 +19749,19 @@
         <v>79</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>115</v>
+        <v>656</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
@@ -19737,19 +19773,19 @@
         <v>79</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>79</v>
+        <v>662</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>79</v>
+        <v>663</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>79</v>
+        <v>664</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>79</v>
@@ -19757,23 +19793,21 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>658</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>659</v>
+        <v>79</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>79</v>
@@ -19785,13 +19819,13 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>660</v>
+        <v>101</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19842,22 +19876,22 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>79</v>
@@ -19874,14 +19908,12 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>79</v>
       </c>
@@ -19890,7 +19922,7 @@
         <v>77</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>79</v>
@@ -19902,13 +19934,13 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>663</v>
+        <v>108</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>664</v>
+        <v>238</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>665</v>
+        <v>239</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19947,16 +19979,16 @@
         <v>79</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF141" t="s" s="2">
         <v>115</v>
@@ -19991,16 +20023,16 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="B142" t="s" s="2">
-        <v>656</v>
-      </c>
       <c r="C142" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>79</v>
+        <v>669</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -20019,13 +20051,13 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>669</v>
+        <v>238</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>670</v>
+        <v>239</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20111,7 +20143,7 @@
         <v>671</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>672</v>
@@ -20139,10 +20171,10 @@
         <v>673</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>290</v>
+        <v>674</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>291</v>
+        <v>675</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -20208,7 +20240,7 @@
         <v>116</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>79</v>
@@ -20225,13 +20257,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>79</v>
@@ -20241,7 +20273,7 @@
         <v>77</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>79</v>
@@ -20253,13 +20285,13 @@
         <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>238</v>
+        <v>679</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>239</v>
+        <v>680</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20342,12 +20374,14 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="D145" t="s" s="2">
         <v>79</v>
       </c>
@@ -20362,26 +20396,22 @@
         <v>79</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>175</v>
+        <v>683</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>678</v>
+        <v>290</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>681</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>79</v>
       </c>
@@ -20393,7 +20423,7 @@
         <v>79</v>
       </c>
       <c r="T145" t="s" s="2">
-        <v>682</v>
+        <v>79</v>
       </c>
       <c r="U145" t="s" s="2">
         <v>79</v>
@@ -20405,13 +20435,13 @@
         <v>79</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>683</v>
+        <v>79</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>684</v>
+        <v>79</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>79</v>
@@ -20429,22 +20459,22 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>685</v>
+        <v>115</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>523</v>
+        <v>236</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>79</v>
@@ -20453,7 +20483,7 @@
         <v>79</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>686</v>
+        <v>79</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20461,12 +20491,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="C146" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>685</v>
+      </c>
       <c r="D146" t="s" s="2">
         <v>79</v>
       </c>
@@ -20484,20 +20516,18 @@
         <v>79</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>175</v>
+        <v>686</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>688</v>
+        <v>238</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>690</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20510,7 +20540,7 @@
         <v>79</v>
       </c>
       <c r="T146" t="s" s="2">
-        <v>691</v>
+        <v>79</v>
       </c>
       <c r="U146" t="s" s="2">
         <v>79</v>
@@ -20522,13 +20552,13 @@
         <v>79</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>692</v>
+        <v>79</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>693</v>
+        <v>79</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>79</v>
@@ -20546,22 +20576,22 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>694</v>
+        <v>115</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>523</v>
+        <v>79</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>79</v>
@@ -20570,7 +20600,7 @@
         <v>79</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>695</v>
+        <v>79</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20578,10 +20608,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20598,25 +20628,25 @@
         <v>79</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J147" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>529</v>
+        <v>691</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20629,7 +20659,7 @@
         <v>79</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>79</v>
@@ -20641,13 +20671,13 @@
         <v>79</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>79</v>
+        <v>693</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>79</v>
+        <v>694</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>79</v>
@@ -20665,7 +20695,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -20680,7 +20710,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>79</v>
@@ -20689,7 +20719,7 @@
         <v>79</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20697,10 +20727,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20711,7 +20741,7 @@
         <v>77</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>79</v>
@@ -20723,15 +20753,17 @@
         <v>88</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N148" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20744,7 +20776,7 @@
         <v>79</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>79</v>
@@ -20756,13 +20788,13 @@
         <v>79</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>79</v>
+        <v>702</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>79</v>
+        <v>703</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>79</v>
@@ -20780,13 +20812,13 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>79</v>
@@ -20795,7 +20827,7 @@
         <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>708</v>
+        <v>523</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>79</v>
@@ -20804,7 +20836,7 @@
         <v>79</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20812,14 +20844,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>711</v>
+        <v>79</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20841,13 +20873,17 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
       </c>
@@ -20859,7 +20895,7 @@
         <v>79</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>79</v>
@@ -20895,7 +20931,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -20910,7 +20946,7 @@
         <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>716</v>
+        <v>531</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -20919,7 +20955,7 @@
         <v>79</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>79</v>
@@ -20927,21 +20963,21 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>719</v>
+        <v>79</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>79</v>
@@ -20956,14 +20992,12 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>722</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>79</v>
@@ -20976,7 +21010,7 @@
         <v>79</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>79</v>
@@ -21012,13 +21046,13 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>79</v>
@@ -21027,7 +21061,7 @@
         <v>99</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>79</v>
@@ -21036,7 +21070,7 @@
         <v>79</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>79</v>
@@ -21044,14 +21078,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>79</v>
+        <v>721</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -21067,16 +21101,16 @@
         <v>79</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -21091,7 +21125,7 @@
         <v>79</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>79</v>
+        <v>724</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>79</v>
@@ -21127,7 +21161,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>104</v>
+        <v>725</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -21139,10 +21173,10 @@
         <v>79</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>79</v>
+        <v>726</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>79</v>
@@ -21151,7 +21185,7 @@
         <v>79</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>79</v>
+        <v>727</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>79</v>
@@ -21159,21 +21193,21 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>79</v>
+        <v>729</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>79</v>
@@ -21182,18 +21216,20 @@
         <v>79</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>238</v>
+        <v>730</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>732</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>79</v>
@@ -21206,7 +21242,7 @@
         <v>79</v>
       </c>
       <c r="T152" t="s" s="2">
-        <v>79</v>
+        <v>733</v>
       </c>
       <c r="U152" t="s" s="2">
         <v>79</v>
@@ -21230,32 +21266,34 @@
         <v>79</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC152" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>115</v>
+        <v>734</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>79</v>
+        <v>735</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>79</v>
@@ -21264,7 +21302,7 @@
         <v>79</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>79</v>
+        <v>736</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>79</v>
@@ -21272,14 +21310,12 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>79</v>
       </c>
@@ -21300,13 +21336,13 @@
         <v>79</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>733</v>
+        <v>101</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21357,19 +21393,19 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>79</v>
@@ -21389,14 +21425,12 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>736</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>79</v>
       </c>
@@ -21405,7 +21439,7 @@
         <v>77</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>79</v>
@@ -21417,13 +21451,13 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>737</v>
+        <v>108</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -21462,16 +21496,14 @@
         <v>79</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC154" s="2"/>
       <c r="AD154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF154" t="s" s="2">
         <v>115</v>
@@ -21489,7 +21521,7 @@
         <v>116</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>79</v>
@@ -21506,12 +21538,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C155" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
       </c>
@@ -21532,13 +21566,13 @@
         <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>101</v>
+        <v>743</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21562,7 +21596,7 @@
         <v>79</v>
       </c>
       <c r="W155" t="s" s="2">
-        <v>741</v>
+        <v>79</v>
       </c>
       <c r="X155" t="s" s="2">
         <v>79</v>
@@ -21589,19 +21623,19 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>742</v>
+        <v>115</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>79</v>
@@ -21621,14 +21655,16 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>746</v>
+      </c>
       <c r="D156" t="s" s="2">
-        <v>744</v>
+        <v>79</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21644,16 +21680,16 @@
         <v>79</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>101</v>
+        <v>747</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>745</v>
+        <v>290</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>746</v>
+        <v>291</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21704,22 +21740,22 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>747</v>
+        <v>115</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>748</v>
+        <v>236</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>79</v>
@@ -21728,7 +21764,7 @@
         <v>79</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>749</v>
+        <v>79</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>79</v>
@@ -21736,14 +21772,14 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>751</v>
+        <v>79</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -21759,16 +21795,16 @@
         <v>79</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21783,7 +21819,7 @@
         <v>79</v>
       </c>
       <c r="T157" t="s" s="2">
-        <v>753</v>
+        <v>79</v>
       </c>
       <c r="U157" t="s" s="2">
         <v>79</v>
@@ -21792,7 +21828,7 @@
         <v>79</v>
       </c>
       <c r="W157" t="s" s="2">
-        <v>79</v>
+        <v>751</v>
       </c>
       <c r="X157" t="s" s="2">
         <v>79</v>
@@ -21819,7 +21855,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>77</v>
@@ -21831,10 +21867,10 @@
         <v>79</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>755</v>
+        <v>79</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>79</v>
@@ -21843,7 +21879,7 @@
         <v>79</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>756</v>
+        <v>79</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21851,14 +21887,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>79</v>
+        <v>754</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21880,14 +21916,12 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>759</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21936,7 +21970,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>77</v>
@@ -21951,7 +21985,7 @@
         <v>99</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>79</v>
@@ -21960,7 +21994,7 @@
         <v>79</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21968,14 +22002,14 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>79</v>
+        <v>761</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -21994,18 +22028,16 @@
         <v>88</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>280</v>
+        <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>766</v>
-      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>79</v>
       </c>
@@ -22017,7 +22049,7 @@
         <v>79</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>79</v>
@@ -22053,7 +22085,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>77</v>
@@ -22068,7 +22100,7 @@
         <v>99</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>566</v>
+        <v>765</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
@@ -22077,7 +22109,7 @@
         <v>79</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>79</v>
@@ -22085,10 +22117,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22108,18 +22140,20 @@
         <v>79</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>102</v>
+        <v>768</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>723</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>769</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>79</v>
@@ -22168,7 +22202,7 @@
         <v>79</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>104</v>
+        <v>770</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>77</v>
@@ -22180,10 +22214,10 @@
         <v>79</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>105</v>
+        <v>771</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>79</v>
@@ -22192,7 +22226,7 @@
         <v>79</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>79</v>
+        <v>772</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>79</v>
@@ -22200,21 +22234,21 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>79</v>
@@ -22223,21 +22257,21 @@
         <v>79</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>109</v>
+        <v>774</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O161" s="2"/>
+        <v>775</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" t="s" s="2">
+        <v>776</v>
+      </c>
       <c r="P161" t="s" s="2">
         <v>79</v>
       </c>
@@ -22249,7 +22283,7 @@
         <v>79</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>79</v>
+        <v>777</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>79</v>
@@ -22273,34 +22307,34 @@
         <v>79</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>115</v>
+        <v>778</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>105</v>
+        <v>566</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>79</v>
@@ -22309,7 +22343,7 @@
         <v>79</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>79</v>
+        <v>779</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>79</v>
@@ -22317,10 +22351,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22340,20 +22374,18 @@
         <v>79</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>773</v>
+        <v>101</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>774</v>
+        <v>102</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>776</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>79</v>
@@ -22402,7 +22434,7 @@
         <v>79</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>777</v>
+        <v>104</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>77</v>
@@ -22411,13 +22443,13 @@
         <v>87</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>778</v>
+        <v>79</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>779</v>
+        <v>105</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>79</v>
@@ -22426,7 +22458,7 @@
         <v>79</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>780</v>
+        <v>79</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>79</v>
@@ -22441,14 +22473,14 @@
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>79</v>
@@ -22457,27 +22489,25 @@
         <v>79</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>773</v>
+        <v>108</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>782</v>
+        <v>109</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>783</v>
+        <v>110</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>784</v>
+        <v>111</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q163" t="s" s="2">
-        <v>785</v>
-      </c>
+      <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
         <v>79</v>
       </c>
@@ -22509,34 +22539,34 @@
         <v>79</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>786</v>
+        <v>115</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>778</v>
+        <v>79</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>787</v>
+        <v>105</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>79</v>
@@ -22545,7 +22575,7 @@
         <v>79</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>788</v>
+        <v>79</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>79</v>
@@ -22553,10 +22583,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22576,21 +22606,21 @@
         <v>79</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>266</v>
+        <v>783</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" t="s" s="2">
-        <v>792</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>79</v>
       </c>
@@ -22614,13 +22644,13 @@
         <v>79</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>793</v>
+        <v>79</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>794</v>
+        <v>79</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>79</v>
@@ -22638,7 +22668,7 @@
         <v>79</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>77</v>
@@ -22647,22 +22677,22 @@
         <v>87</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>79</v>
+        <v>788</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>796</v>
+        <v>79</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>79</v>
@@ -22670,10 +22700,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22693,27 +22723,27 @@
         <v>79</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>803</v>
-      </c>
+        <v>794</v>
+      </c>
+      <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q165" s="2"/>
+      <c r="Q165" t="s" s="2">
+        <v>795</v>
+      </c>
       <c r="R165" t="s" s="2">
         <v>79</v>
       </c>
@@ -22757,7 +22787,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -22766,22 +22796,22 @@
         <v>87</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>79</v>
+        <v>788</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>79</v>
@@ -22789,10 +22819,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22803,7 +22833,7 @@
         <v>77</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>79</v>
@@ -22815,19 +22845,17 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>807</v>
+        <v>266</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>810</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>79</v>
@@ -22852,13 +22880,13 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>79</v>
+        <v>803</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>79</v>
+        <v>804</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22876,13 +22904,13 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>79</v>
@@ -22891,16 +22919,16 @@
         <v>99</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>105</v>
+        <v>806</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>79</v>
@@ -22908,10 +22936,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22922,7 +22950,7 @@
         <v>77</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>79</v>
@@ -22934,19 +22962,19 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22995,22 +23023,22 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK167" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI167" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="AK167" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>105</v>
@@ -23019,7 +23047,7 @@
         <v>79</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>79</v>
+        <v>815</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23027,10 +23055,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23041,7 +23069,7 @@
         <v>77</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>79</v>
@@ -23053,16 +23081,20 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>101</v>
+        <v>817</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>102</v>
+        <v>818</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>819</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>821</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
       </c>
@@ -23110,31 +23142,31 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>104</v>
+        <v>816</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK168" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AL168" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AL168" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>79</v>
+        <v>823</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23142,10 +23174,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23168,16 +23200,20 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>108</v>
+        <v>825</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>238</v>
+        <v>826</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
+        <v>827</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>829</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
       </c>
@@ -23213,17 +23249,19 @@
         <v>79</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC169" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>115</v>
+        <v>824</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>77</v>
@@ -23235,13 +23273,13 @@
         <v>79</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>116</v>
+        <v>830</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>79</v>
+        <v>831</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>79</v>
@@ -23255,14 +23293,12 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>825</v>
-      </c>
+        <v>832</v>
+      </c>
+      <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>79</v>
       </c>
@@ -23271,7 +23307,7 @@
         <v>77</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>79</v>
@@ -23283,13 +23319,13 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>826</v>
+        <v>101</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>290</v>
+        <v>102</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>291</v>
+        <v>103</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23340,22 +23376,22 @@
         <v>79</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>79</v>
@@ -23372,14 +23408,12 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>828</v>
-      </c>
+        <v>833</v>
+      </c>
+      <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>79</v>
       </c>
@@ -23400,13 +23434,13 @@
         <v>79</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>829</v>
+        <v>108</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23445,16 +23479,14 @@
         <v>79</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC171" s="2"/>
       <c r="AD171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF171" t="s" s="2">
         <v>115</v>
@@ -23466,13 +23498,13 @@
         <v>78</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>79</v>
@@ -23489,14 +23521,16 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C172" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>835</v>
+      </c>
       <c r="D172" t="s" s="2">
-        <v>831</v>
+        <v>79</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -23509,26 +23543,22 @@
         <v>79</v>
       </c>
       <c r="I172" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>108</v>
+        <v>836</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>832</v>
+        <v>290</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>79</v>
       </c>
@@ -23576,7 +23606,7 @@
         <v>79</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>834</v>
+        <v>115</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>77</v>
@@ -23585,7 +23615,7 @@
         <v>78</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>116</v>
@@ -23608,12 +23638,14 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="C173" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>838</v>
+      </c>
       <c r="D173" t="s" s="2">
         <v>79</v>
       </c>
@@ -23634,18 +23666,16 @@
         <v>79</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>266</v>
+        <v>839</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>836</v>
+        <v>290</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>837</v>
+        <v>291</v>
       </c>
       <c r="N173" s="2"/>
-      <c r="O173" t="s" s="2">
-        <v>838</v>
-      </c>
+      <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>79</v>
       </c>
@@ -23669,13 +23699,13 @@
         <v>79</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>839</v>
+        <v>79</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>840</v>
+        <v>79</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>79</v>
@@ -23693,7 +23723,7 @@
         <v>79</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>835</v>
+        <v>115</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>77</v>
@@ -23702,22 +23732,22 @@
         <v>78</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>841</v>
+        <v>79</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>79</v>
@@ -23725,42 +23755,46 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>79</v>
+        <v>841</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I174" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>102</v>
+        <v>842</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>79</v>
       </c>
@@ -23808,22 +23842,22 @@
         <v>79</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>104</v>
+        <v>844</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>79</v>
@@ -23840,14 +23874,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23866,18 +23900,18 @@
         <v>79</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>108</v>
+        <v>266</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>109</v>
+        <v>846</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O175" s="2"/>
+        <v>847</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" t="s" s="2">
+        <v>848</v>
+      </c>
       <c r="P175" t="s" s="2">
         <v>79</v>
       </c>
@@ -23901,31 +23935,31 @@
         <v>79</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>79</v>
+        <v>849</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>79</v>
+        <v>850</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>115</v>
+        <v>845</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>77</v>
@@ -23937,19 +23971,19 @@
         <v>79</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK175" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL175" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AL175" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>79</v>
+        <v>851</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>79</v>
@@ -23957,10 +23991,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23971,7 +24005,7 @@
         <v>77</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>79</v>
@@ -23980,23 +24014,19 @@
         <v>79</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>438</v>
+        <v>102</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>79</v>
       </c>
@@ -24032,32 +24062,34 @@
         <v>79</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AC176" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>442</v>
+        <v>104</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>79</v>
@@ -24066,7 +24098,7 @@
         <v>79</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>79</v>
@@ -24074,16 +24106,14 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>846</v>
-      </c>
+        <v>853</v>
+      </c>
+      <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -24099,23 +24129,21 @@
         <v>79</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>438</v>
+        <v>109</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>439</v>
+        <v>110</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>79</v>
       </c>
@@ -24151,19 +24179,19 @@
         <v>79</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>442</v>
+        <v>115</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>77</v>
@@ -24175,10 +24203,10 @@
         <v>79</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>79</v>
@@ -24187,7 +24215,7 @@
         <v>79</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24195,10 +24223,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24209,7 +24237,7 @@
         <v>77</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>79</v>
@@ -24218,19 +24246,23 @@
         <v>79</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>102</v>
+        <v>438</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
       </c>
@@ -24266,34 +24298,32 @@
         <v>79</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>104</v>
+        <v>442</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>79</v>
@@ -24302,7 +24332,7 @@
         <v>79</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24310,14 +24340,16 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>854</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>856</v>
+      </c>
       <c r="D179" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -24333,21 +24365,23 @@
         <v>79</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>109</v>
+        <v>438</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>110</v>
+        <v>439</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
       </c>
@@ -24383,19 +24417,19 @@
         <v>79</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>115</v>
+        <v>442</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>77</v>
@@ -24407,10 +24441,10 @@
         <v>79</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>79</v>
@@ -24419,7 +24453,7 @@
         <v>79</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>79</v>
@@ -24427,10 +24461,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24438,7 +24472,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>87</v>
@@ -24450,29 +24484,25 @@
         <v>79</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>853</v>
+        <v>79</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>79</v>
@@ -24514,7 +24544,7 @@
         <v>79</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>77</v>
@@ -24526,10 +24556,10 @@
         <v>79</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>79</v>
@@ -24538,7 +24568,7 @@
         <v>79</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>79</v>
@@ -24546,21 +24576,21 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>79</v>
@@ -24569,19 +24599,19 @@
         <v>79</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -24619,34 +24649,34 @@
         <v>79</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>79</v>
@@ -24655,7 +24685,7 @@
         <v>79</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>79</v>
@@ -24663,10 +24693,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24674,7 +24704,7 @@
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>87</v>
@@ -24689,24 +24719,26 @@
         <v>88</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>457</v>
+        <v>158</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="N182" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O182" t="s" s="2">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>79</v>
+        <v>863</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>79</v>
@@ -24748,7 +24780,7 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>77</v>
@@ -24763,7 +24795,7 @@
         <v>99</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>79</v>
@@ -24772,7 +24804,7 @@
         <v>79</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>79</v>
@@ -24780,10 +24812,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24809,15 +24841,15 @@
         <v>101</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>79</v>
       </c>
@@ -24865,7 +24897,7 @@
         <v>79</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>77</v>
@@ -24880,7 +24912,7 @@
         <v>99</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>79</v>
@@ -24889,7 +24921,7 @@
         <v>79</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>79</v>
@@ -24897,10 +24929,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24923,19 +24955,17 @@
         <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>193</v>
+        <v>457</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>79</v>
@@ -24984,7 +25014,7 @@
         <v>79</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>77</v>
@@ -24999,7 +25029,7 @@
         <v>99</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>79</v>
@@ -25008,7 +25038,7 @@
         <v>79</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>79</v>
@@ -25016,10 +25046,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25045,16 +25075,14 @@
         <v>101</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>465</v>
+        <v>184</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>468</v>
+        <v>186</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>79</v>
@@ -25103,7 +25131,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>469</v>
+        <v>187</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>77</v>
@@ -25118,7 +25146,7 @@
         <v>99</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>470</v>
+        <v>188</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>79</v>
@@ -25127,7 +25155,7 @@
         <v>79</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>471</v>
+        <v>189</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>79</v>
@@ -25135,10 +25163,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25158,20 +25186,22 @@
         <v>79</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>500</v>
+        <v>192</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>865</v>
+        <v>193</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N186" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O186" t="s" s="2">
-        <v>867</v>
+        <v>196</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>79</v>
@@ -25220,7 +25250,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>864</v>
+        <v>197</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>77</v>
@@ -25235,16 +25265,16 @@
         <v>99</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>505</v>
+        <v>198</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>868</v>
+        <v>199</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>79</v>
@@ -25252,10 +25282,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25266,7 +25296,7 @@
         <v>77</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>79</v>
@@ -25275,22 +25305,22 @@
         <v>79</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>569</v>
+        <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>870</v>
+        <v>465</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>871</v>
+        <v>466</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>872</v>
+        <v>467</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>573</v>
+        <v>468</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25339,13 +25369,13 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>869</v>
+        <v>469</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>79</v>
@@ -25354,16 +25384,16 @@
         <v>99</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>574</v>
+        <v>470</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>873</v>
+        <v>471</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25397,7 +25427,7 @@
         <v>79</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>647</v>
+        <v>500</v>
       </c>
       <c r="L188" t="s" s="2">
         <v>875</v>
@@ -25471,7 +25501,7 @@
         <v>99</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>652</v>
+        <v>505</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>105</v>
@@ -25502,7 +25532,7 @@
         <v>77</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>79</v>
@@ -25514,17 +25544,19 @@
         <v>79</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>175</v>
+        <v>569</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>619</v>
+        <v>880</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="N189" s="2"/>
+        <v>881</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>882</v>
+      </c>
       <c r="O189" t="s" s="2">
-        <v>881</v>
+        <v>573</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -25549,13 +25581,13 @@
         <v>79</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>79</v>
@@ -25579,7 +25611,7 @@
         <v>77</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>79</v>
@@ -25588,7 +25620,7 @@
         <v>99</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>625</v>
+        <v>574</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>105</v>
@@ -25597,7 +25629,7 @@
         <v>79</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>79</v>
@@ -25605,10 +25637,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25631,7 +25663,7 @@
         <v>79</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>884</v>
+        <v>657</v>
       </c>
       <c r="L190" t="s" s="2">
         <v>885</v>
@@ -25690,7 +25722,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>77</v>
@@ -25699,13 +25731,13 @@
         <v>87</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>888</v>
+        <v>79</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>889</v>
+        <v>662</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>105</v>
@@ -25714,7 +25746,7 @@
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25722,10 +25754,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25748,16 +25780,18 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>892</v>
+        <v>629</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
+      <c r="O191" t="s" s="2">
+        <v>891</v>
+      </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
       </c>
@@ -25781,13 +25815,13 @@
         <v>79</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>79</v>
+        <v>633</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>79</v>
+        <v>634</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>79</v>
@@ -25805,7 +25839,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -25820,7 +25854,7 @@
         <v>99</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>894</v>
+        <v>635</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>105</v>
@@ -25829,7 +25863,7 @@
         <v>79</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>79</v>
+        <v>892</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>79</v>
@@ -25837,10 +25871,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25851,7 +25885,7 @@
         <v>77</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>79</v>
@@ -25863,19 +25897,17 @@
         <v>79</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>815</v>
+        <v>894</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>896</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" s="2"/>
+      <c r="O192" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>79</v>
@@ -25924,31 +25956,31 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>79</v>
+        <v>898</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK192" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN192" t="s" s="2">
         <v>900</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>79</v>
@@ -25956,10 +25988,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25982,13 +26014,13 @@
         <v>79</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>102</v>
+        <v>902</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>103</v>
+        <v>903</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -26039,7 +26071,7 @@
         <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>104</v>
+        <v>901</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>77</v>
@@ -26051,13 +26083,13 @@
         <v>79</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK193" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="AL193" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>79</v>
@@ -26071,14 +26103,14 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -26097,18 +26129,20 @@
         <v>79</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>108</v>
+        <v>825</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>109</v>
+        <v>906</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>110</v>
+        <v>907</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O194" s="2"/>
+        <v>908</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>909</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>79</v>
       </c>
@@ -26156,7 +26190,7 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>115</v>
+        <v>905</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>77</v>
@@ -26168,13 +26202,13 @@
         <v>79</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>105</v>
+        <v>910</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>79</v>
+        <v>911</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>79</v>
@@ -26188,46 +26222,42 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>831</v>
+        <v>79</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I195" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>832</v>
+        <v>102</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>79</v>
       </c>
@@ -26275,22 +26305,22 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>834</v>
+        <v>104</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>79</v>
@@ -26307,21 +26337,21 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>79</v>
@@ -26333,20 +26363,18 @@
         <v>79</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>266</v>
+        <v>108</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>906</v>
+        <v>109</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>907</v>
+        <v>110</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>909</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>79</v>
       </c>
@@ -26370,13 +26398,13 @@
         <v>79</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>79</v>
@@ -26394,31 +26422,31 @@
         <v>79</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>905</v>
+        <v>115</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>910</v>
+        <v>105</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>911</v>
+        <v>79</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>912</v>
+        <v>79</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>79</v>
@@ -26426,42 +26454,46 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>79</v>
+        <v>841</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>102</v>
+        <v>842</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>79</v>
       </c>
@@ -26509,22 +26541,22 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>104</v>
+        <v>844</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>79</v>
@@ -26541,21 +26573,21 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>79</v>
@@ -26567,18 +26599,20 @@
         <v>79</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>108</v>
+        <v>266</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>109</v>
+        <v>916</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>110</v>
+        <v>917</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O198" s="2"/>
+        <v>918</v>
+      </c>
+      <c r="O198" t="s" s="2">
+        <v>919</v>
+      </c>
       <c r="P198" t="s" s="2">
         <v>79</v>
       </c>
@@ -26602,55 +26636,55 @@
         <v>79</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC198" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE198" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>115</v>
+        <v>915</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>105</v>
+        <v>920</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>79</v>
+        <v>921</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>79</v>
+        <v>922</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>79</v>
@@ -26658,10 +26692,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26672,7 +26706,7 @@
         <v>77</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>79</v>
@@ -26681,23 +26715,19 @@
         <v>79</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>438</v>
+        <v>102</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N199" s="2"/>
+      <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>79</v>
       </c>
@@ -26733,32 +26763,34 @@
         <v>79</v>
       </c>
       <c r="AB199" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AC199" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC199" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD199" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE199" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>442</v>
+        <v>104</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="AL199" t="s" s="2">
         <v>79</v>
@@ -26767,7 +26799,7 @@
         <v>79</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>79</v>
@@ -26775,16 +26807,14 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>917</v>
-      </c>
+        <v>924</v>
+      </c>
+      <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -26800,23 +26830,21 @@
         <v>79</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>438</v>
+        <v>109</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>439</v>
+        <v>110</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>79</v>
       </c>
@@ -26852,19 +26880,19 @@
         <v>79</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>442</v>
+        <v>115</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>77</v>
@@ -26876,10 +26904,10 @@
         <v>79</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="AL200" t="s" s="2">
         <v>79</v>
@@ -26888,7 +26916,7 @@
         <v>79</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>79</v>
@@ -26896,10 +26924,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26910,7 +26938,7 @@
         <v>77</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>79</v>
@@ -26919,19 +26947,23 @@
         <v>79</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>102</v>
+        <v>438</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N201" s="2"/>
-      <c r="O201" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O201" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P201" t="s" s="2">
         <v>79</v>
       </c>
@@ -26967,34 +26999,32 @@
         <v>79</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>104</v>
+        <v>442</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>79</v>
@@ -27003,7 +27033,7 @@
         <v>79</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>79</v>
@@ -27011,14 +27041,16 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="C202" s="2"/>
+        <v>925</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>927</v>
+      </c>
       <c r="D202" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
@@ -27034,21 +27066,23 @@
         <v>79</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>109</v>
+        <v>438</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>110</v>
+        <v>439</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O202" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O202" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>79</v>
       </c>
@@ -27084,19 +27118,19 @@
         <v>79</v>
       </c>
       <c r="AB202" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC202" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE202" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>115</v>
+        <v>442</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>77</v>
@@ -27108,10 +27142,10 @@
         <v>79</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>79</v>
@@ -27120,7 +27154,7 @@
         <v>79</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>79</v>
@@ -27128,14 +27162,12 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>923</v>
-      </c>
+        <v>929</v>
+      </c>
+      <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
         <v>79</v>
       </c>
@@ -27156,13 +27188,13 @@
         <v>79</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>924</v>
+        <v>101</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>925</v>
+        <v>102</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>926</v>
+        <v>103</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -27213,22 +27245,22 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>79</v>
@@ -27245,21 +27277,21 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>79</v>
@@ -27271,15 +27303,17 @@
         <v>79</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N204" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N204" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>79</v>
@@ -27316,31 +27350,31 @@
         <v>79</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>105</v>
@@ -27360,12 +27394,14 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>931</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>933</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
       </c>
@@ -27374,7 +27410,7 @@
         <v>77</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>79</v>
@@ -27386,13 +27422,13 @@
         <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>108</v>
+        <v>934</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>238</v>
+        <v>935</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>239</v>
+        <v>936</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -27431,16 +27467,16 @@
         <v>79</v>
       </c>
       <c r="AB205" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC205" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD205" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE205" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
         <v>115</v>
@@ -27475,10 +27511,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27486,7 +27522,7 @@
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G206" t="s" s="2">
         <v>87</v>
@@ -27501,24 +27537,22 @@
         <v>79</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q206" s="2"/>
       <c r="R206" t="s" s="2">
-        <v>933</v>
+        <v>79</v>
       </c>
       <c r="S206" t="s" s="2">
         <v>79</v>
@@ -27560,10 +27594,10 @@
         <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>87</v>
@@ -27575,7 +27609,7 @@
         <v>79</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AL206" t="s" s="2">
         <v>79</v>
@@ -27592,10 +27626,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27606,7 +27640,7 @@
         <v>77</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>79</v>
@@ -27618,13 +27652,13 @@
         <v>79</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>936</v>
+        <v>108</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>937</v>
+        <v>239</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27663,32 +27697,34 @@
         <v>79</v>
       </c>
       <c r="AB207" t="s" s="2">
-        <v>938</v>
-      </c>
-      <c r="AC207" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="AC207" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE207" t="s" s="2">
-        <v>939</v>
+        <v>114</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>79</v>
@@ -27705,20 +27741,18 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="C208" t="s" s="2">
-        <v>941</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G208" t="s" s="2">
         <v>87</v>
@@ -27733,22 +27767,24 @@
         <v>79</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="N208" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>79</v>
+        <v>943</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>79</v>
@@ -27790,10 +27826,10 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>87</v>
@@ -27802,7 +27838,7 @@
         <v>79</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>236</v>
@@ -27822,10 +27858,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27833,7 +27869,7 @@
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G209" t="s" s="2">
         <v>87</v>
@@ -27845,29 +27881,25 @@
         <v>79</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>129</v>
+        <v>946</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="N209" s="2"/>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q209" s="2"/>
       <c r="R209" t="s" s="2">
-        <v>945</v>
+        <v>79</v>
       </c>
       <c r="S209" t="s" s="2">
         <v>79</v>
@@ -27897,19 +27929,17 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC209" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>948</v>
+      </c>
+      <c r="AC209" s="2"/>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>79</v>
+        <v>949</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -27924,7 +27954,7 @@
         <v>99</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>79</v>
@@ -27933,7 +27963,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -27941,12 +27971,14 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>947</v>
-      </c>
-      <c r="C210" s="2"/>
+        <v>945</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>951</v>
+      </c>
       <c r="D210" t="s" s="2">
         <v>79</v>
       </c>
@@ -27964,20 +27996,18 @@
         <v>79</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>952</v>
+      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>79</v>
@@ -28026,7 +28056,7 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -28041,7 +28071,7 @@
         <v>99</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="AL210" t="s" s="2">
         <v>79</v>
@@ -28050,7 +28080,7 @@
         <v>79</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>79</v>
@@ -28058,10 +28088,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28069,7 +28099,7 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>87</v>
@@ -28084,24 +28114,26 @@
         <v>88</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>457</v>
+        <v>158</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="N211" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O211" t="s" s="2">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q211" s="2"/>
       <c r="R211" t="s" s="2">
-        <v>79</v>
+        <v>955</v>
       </c>
       <c r="S211" t="s" s="2">
         <v>79</v>
@@ -28143,7 +28175,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>77</v>
@@ -28158,7 +28190,7 @@
         <v>99</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>79</v>
@@ -28167,7 +28199,7 @@
         <v>79</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>79</v>
@@ -28175,10 +28207,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28204,15 +28236,15 @@
         <v>101</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N212" s="2"/>
-      <c r="O212" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>79</v>
       </c>
@@ -28260,7 +28292,7 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -28275,7 +28307,7 @@
         <v>99</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>79</v>
@@ -28284,7 +28316,7 @@
         <v>79</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>79</v>
@@ -28292,10 +28324,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28318,19 +28350,17 @@
         <v>88</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>193</v>
+        <v>457</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>79</v>
@@ -28379,7 +28409,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>77</v>
@@ -28394,7 +28424,7 @@
         <v>99</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>79</v>
@@ -28403,7 +28433,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28411,14 +28441,12 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="C214" t="s" s="2">
-        <v>955</v>
-      </c>
+        <v>961</v>
+      </c>
+      <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
         <v>79</v>
       </c>
@@ -28427,7 +28455,7 @@
         <v>77</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>79</v>
@@ -28439,19 +28467,17 @@
         <v>88</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>438</v>
+        <v>184</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>441</v>
+        <v>186</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28476,11 +28502,13 @@
         <v>79</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="Y214" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z214" t="s" s="2">
-        <v>956</v>
+        <v>79</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>79</v>
@@ -28498,13 +28526,13 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>442</v>
+        <v>187</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>79</v>
@@ -28513,7 +28541,7 @@
         <v>99</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>443</v>
+        <v>188</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>79</v>
@@ -28522,7 +28550,7 @@
         <v>79</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>444</v>
+        <v>189</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
@@ -28530,10 +28558,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>919</v>
+        <v>963</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28553,19 +28581,23 @@
         <v>79</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N215" s="2"/>
-      <c r="O215" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O215" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>79</v>
       </c>
@@ -28613,7 +28645,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>77</v>
@@ -28625,10 +28657,10 @@
         <v>79</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>79</v>
@@ -28637,7 +28669,7 @@
         <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28645,14 +28677,16 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="C216" s="2"/>
+        <v>925</v>
+      </c>
+      <c r="C216" t="s" s="2">
+        <v>965</v>
+      </c>
       <c r="D216" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
@@ -28668,21 +28702,23 @@
         <v>79</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>109</v>
+        <v>438</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>110</v>
+        <v>439</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
       </c>
@@ -28706,31 +28742,29 @@
         <v>79</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y216" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>79</v>
+        <v>966</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>115</v>
+        <v>442</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>77</v>
@@ -28742,10 +28776,10 @@
         <v>79</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>79</v>
@@ -28754,7 +28788,7 @@
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -28762,10 +28796,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>944</v>
+        <v>929</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28773,7 +28807,7 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>87</v>
@@ -28785,23 +28819,19 @@
         <v>79</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>79</v>
       </c>
@@ -28849,7 +28879,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>77</v>
@@ -28861,10 +28891,10 @@
         <v>79</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="AL217" t="s" s="2">
         <v>79</v>
@@ -28873,7 +28903,7 @@
         <v>79</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>79</v>
@@ -28881,21 +28911,21 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>79</v>
@@ -28904,19 +28934,19 @@
         <v>79</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
@@ -28954,34 +28984,34 @@
         <v>79</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI218" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>79</v>
@@ -28990,7 +29020,7 @@
         <v>79</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>79</v>
@@ -28998,10 +29028,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29009,7 +29039,7 @@
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G219" t="s" s="2">
         <v>87</v>
@@ -29024,17 +29054,19 @@
         <v>88</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>457</v>
+        <v>158</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="N219" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O219" t="s" s="2">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>79</v>
@@ -29083,7 +29115,7 @@
         <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>77</v>
@@ -29098,7 +29130,7 @@
         <v>99</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AL219" t="s" s="2">
         <v>79</v>
@@ -29107,7 +29139,7 @@
         <v>79</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>79</v>
@@ -29115,10 +29147,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29144,15 +29176,15 @@
         <v>101</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N220" s="2"/>
-      <c r="O220" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N220" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29200,7 +29232,7 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>77</v>
@@ -29215,7 +29247,7 @@
         <v>99</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>79</v>
@@ -29224,7 +29256,7 @@
         <v>79</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="AO220" t="s" s="2">
         <v>79</v>
@@ -29232,10 +29264,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29258,19 +29290,17 @@
         <v>88</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>193</v>
+        <v>457</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>79</v>
@@ -29319,7 +29349,7 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>77</v>
@@ -29334,7 +29364,7 @@
         <v>99</v>
       </c>
       <c r="AK221" t="s" s="2">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AL221" t="s" s="2">
         <v>79</v>
@@ -29343,7 +29373,7 @@
         <v>79</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>79</v>
@@ -29351,10 +29381,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29380,16 +29410,14 @@
         <v>101</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>465</v>
+        <v>184</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>468</v>
+        <v>186</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>79</v>
@@ -29438,7 +29466,7 @@
         <v>79</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>469</v>
+        <v>187</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>77</v>
@@ -29453,7 +29481,7 @@
         <v>99</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>470</v>
+        <v>188</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>79</v>
@@ -29462,7 +29490,7 @@
         <v>79</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>471</v>
+        <v>189</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>79</v>
@@ -29470,10 +29498,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29493,22 +29521,22 @@
         <v>79</v>
       </c>
       <c r="J223" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K223" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>966</v>
+        <v>193</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>967</v>
+        <v>194</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>968</v>
+        <v>195</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>969</v>
+        <v>196</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>79</v>
@@ -29557,7 +29585,7 @@
         <v>79</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>965</v>
+        <v>197</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>77</v>
@@ -29572,16 +29600,16 @@
         <v>99</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>970</v>
+        <v>198</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>971</v>
+        <v>79</v>
       </c>
       <c r="AM223" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>972</v>
+        <v>199</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>79</v>
@@ -29589,21 +29617,21 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>974</v>
+        <v>79</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>79</v>
@@ -29612,21 +29640,23 @@
         <v>79</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>975</v>
+        <v>101</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>976</v>
+        <v>465</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>977</v>
+        <v>466</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="O224" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="O224" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P224" t="s" s="2">
         <v>79</v>
       </c>
@@ -29674,13 +29704,13 @@
         <v>79</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>973</v>
+        <v>469</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>79</v>
@@ -29689,16 +29719,16 @@
         <v>99</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>979</v>
+        <v>470</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM224" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>980</v>
+        <v>471</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>79</v>
@@ -29706,10 +29736,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29729,22 +29759,22 @@
         <v>79</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>982</v>
+        <v>192</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>79</v>
@@ -29793,7 +29823,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>77</v>
@@ -29808,16 +29838,16 @@
         <v>99</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>889</v>
+        <v>980</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>79</v>
+        <v>982</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>79</v>
@@ -29825,14 +29855,14 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>79</v>
+        <v>984</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
@@ -29845,26 +29875,24 @@
         <v>79</v>
       </c>
       <c r="I226" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>815</v>
+        <v>985</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>992</v>
-      </c>
+        <v>988</v>
+      </c>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>79</v>
       </c>
@@ -29912,7 +29940,7 @@
         <v>79</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>77</v>
@@ -29927,7 +29955,7 @@
         <v>99</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="AL226" t="s" s="2">
         <v>105</v>
@@ -29936,7 +29964,7 @@
         <v>79</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>79</v>
+        <v>990</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>79</v>
@@ -29944,10 +29972,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29967,19 +29995,23 @@
         <v>79</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>101</v>
+        <v>992</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>102</v>
+        <v>993</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N227" s="2"/>
-      <c r="O227" s="2"/>
+        <v>994</v>
+      </c>
+      <c r="N227" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="O227" t="s" s="2">
+        <v>996</v>
+      </c>
       <c r="P227" t="s" s="2">
         <v>79</v>
       </c>
@@ -30027,7 +30059,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>104</v>
+        <v>991</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>77</v>
@@ -30039,13 +30071,13 @@
         <v>79</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>105</v>
+        <v>899</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>79</v>
+        <v>997</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>79</v>
@@ -30059,14 +30091,14 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
@@ -30079,24 +30111,26 @@
         <v>79</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>108</v>
+        <v>825</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>109</v>
+        <v>999</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O228" s="2"/>
+        <v>1001</v>
+      </c>
+      <c r="O228" t="s" s="2">
+        <v>1002</v>
+      </c>
       <c r="P228" t="s" s="2">
         <v>79</v>
       </c>
@@ -30144,7 +30178,7 @@
         <v>79</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>115</v>
+        <v>998</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>77</v>
@@ -30156,13 +30190,13 @@
         <v>79</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK228" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="AL228" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="AL228" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>79</v>
@@ -30176,46 +30210,42 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>831</v>
+        <v>79</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I229" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>832</v>
+        <v>102</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>79</v>
       </c>
@@ -30263,22 +30293,22 @@
         <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>834</v>
+        <v>104</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AL229" t="s" s="2">
         <v>79</v>
@@ -30295,21 +30325,21 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>79</v>
@@ -30318,19 +30348,19 @@
         <v>79</v>
       </c>
       <c r="J230" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>998</v>
+        <v>108</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>999</v>
+        <v>109</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>1001</v>
+        <v>111</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -30380,31 +30410,31 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>997</v>
+        <v>115</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>317</v>
+        <v>105</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>1002</v>
+        <v>79</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>79</v>
@@ -30412,42 +30442,46 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>79</v>
+        <v>841</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I231" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J231" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>1004</v>
+        <v>842</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>1005</v>
-      </c>
-      <c r="N231" s="2"/>
-      <c r="O231" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="N231" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O231" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P231" t="s" s="2">
         <v>79</v>
       </c>
@@ -30471,57 +30505,289 @@
         <v>79</v>
       </c>
       <c r="X231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF231" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="AG231" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH231" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ231" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK231" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AL231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN231" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO231" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="C232" s="2"/>
+      <c r="D232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E232" s="2"/>
+      <c r="F232" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G232" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J232" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K232" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="L232" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="M232" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="N232" t="s" s="2">
+        <v>1011</v>
+      </c>
+      <c r="O232" s="2"/>
+      <c r="P232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q232" s="2"/>
+      <c r="R232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF232" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="AG232" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH232" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ232" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK232" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL232" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM232" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN232" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="AO232" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C233" s="2"/>
+      <c r="D233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E233" s="2"/>
+      <c r="F233" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G233" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J233" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K233" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L233" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="M233" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="N233" s="2"/>
+      <c r="O233" s="2"/>
+      <c r="P233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q233" s="2"/>
+      <c r="R233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X233" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y231" t="s" s="2">
-        <v>1005</v>
-      </c>
-      <c r="Z231" t="s" s="2">
-        <v>1006</v>
-      </c>
-      <c r="AA231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF231" t="s" s="2">
-        <v>1003</v>
-      </c>
-      <c r="AG231" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH231" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ231" t="s" s="2">
+      <c r="Y233" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="Z233" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="AA233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF233" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="AG233" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH233" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ233" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK231" t="s" s="2">
-        <v>1007</v>
-      </c>
-      <c r="AL231" t="s" s="2">
+      <c r="AK233" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="AL233" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AM231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN231" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO231" t="s" s="2">
+      <c r="AM233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN233" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO233" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:30:20+00:00</t>
+    <t>2026-09-15T05:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8665" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8666" uniqueCount="1019">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T05:06:55+00:00</t>
+    <t>2026-09-17T19:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -777,16 +777,16 @@
     <t>The patient's legal status as citizen of a country.</t>
   </si>
   <si>
-    <t>Patient.extension:citizenship.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:citizenship.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
     <t>Patient.extension:citizenship.extension</t>
   </si>
   <si>
@@ -846,17 +846,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/country</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:citizenship.extension:period</t>
@@ -903,7 +896,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Patient.extension:deathRegisteredTime</t>
@@ -1337,7 +1330,7 @@
     <t>A locally assigned H-nummer</t>
   </si>
   <si>
-    <t>A locally assigned H-nummer. If this identifier is used, information about the assigner is mandatory.</t>
+    <t>A locally assigned H-nummer. If this identifier is used, information about the assigner is mandatory. Merk at lokale hjelpenummer (H-nummer) for pasient ikke garanterer at kombinasjonen system og value er gir unik identifikasjon, siden disse tildeles på lokalt i det enkelte kliniske fagsystem. Felles nasjonale hjelpenummer utstedt av tjenesten for felles hjelpenummer er imidlertid unike i Norge (og globalt unike i kombinasjon med system).</t>
   </si>
   <si>
     <t>Patient.identifier:HNR.id</t>
@@ -1597,6 +1590,10 @@
     <t>middlename</t>
   </si>
   <si>
+    <t xml:space="preserve">mellomnavn
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-middlename}
 </t>
   </si>
@@ -2090,10 +2087,20 @@
 </t>
   </si>
   <si>
+    <t>The concept of an officially registered address</t>
+  </si>
+  <si>
+    <t>Defines the concept of an officially registered address in Norway. Usually this will be the adress registered in "Folkeregisteret" for persons or "Enhetsregisteret" for organizations.</t>
+  </si>
+  <si>
     <t>Patient.address.extension:urbanDistrict</t>
   </si>
   <si>
     <t>urbanDistrict</t>
+  </si>
+  <si>
+    <t>bydel
+urban district</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/StructureDefinition/no-basis-urban-district}
@@ -2944,10 +2951,6 @@
   </si>
   <si>
     <t>Patient.communication.language.coding.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
@@ -6533,7 +6536,7 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>116</v>
@@ -6556,10 +6559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6582,7 +6585,7 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>102</v>
@@ -6648,7 +6651,7 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>79</v>
@@ -6929,7 +6932,7 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>102</v>
@@ -6995,7 +6998,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>79</v>
@@ -7309,30 +7312,32 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
@@ -7340,7 +7345,7 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
@@ -7363,13 +7368,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>250</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -7394,10 +7399,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7480,7 +7485,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>255</v>
@@ -7506,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>102</v>
@@ -7572,7 +7577,7 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>79</v>
@@ -7595,7 +7600,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>257</v>
@@ -7710,7 +7715,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>259</v>
@@ -7753,7 +7758,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>79</v>
@@ -7827,7 +7832,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>265</v>
@@ -7853,7 +7858,7 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>267</v>
@@ -7910,7 +7915,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -7919,7 +7924,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -7942,10 +7947,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7985,7 +7990,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -8059,10 +8064,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8085,7 +8090,7 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>267</v>
@@ -8142,7 +8147,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -8151,7 +8156,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -8174,13 +8179,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>79</v>
@@ -8202,13 +8207,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -8291,13 +8296,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>79</v>
@@ -8319,13 +8324,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8408,13 +8413,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>79</v>
@@ -8436,13 +8441,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8525,13 +8530,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>79</v>
@@ -8553,13 +8558,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8642,13 +8647,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>79</v>
@@ -8670,13 +8675,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8759,13 +8764,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>237</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>79</v>
@@ -8787,13 +8792,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8876,10 +8881,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8905,16 +8910,16 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -8963,7 +8968,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -8995,10 +9000,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9021,17 +9026,17 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -9078,7 +9083,7 @@
         <v>114</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -9093,16 +9098,16 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -9110,10 +9115,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9225,10 +9230,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9342,10 +9347,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9371,16 +9376,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9405,31 +9410,31 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -9444,7 +9449,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -9461,10 +9466,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9490,16 +9495,16 @@
         <v>266</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9527,28 +9532,28 @@
         <v>145</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -9563,7 +9568,7 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>79</v>
@@ -9572,7 +9577,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9580,10 +9585,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9609,16 +9614,16 @@
         <v>129</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -9631,7 +9636,7 @@
         <v>79</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>79</v>
@@ -9667,7 +9672,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -9682,7 +9687,7 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>79</v>
@@ -9691,7 +9696,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -9699,10 +9704,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9728,13 +9733,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9748,7 +9753,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -9784,7 +9789,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -9799,7 +9804,7 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
@@ -9808,7 +9813,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -9816,10 +9821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9842,13 +9847,13 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9899,7 +9904,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -9914,7 +9919,7 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>79</v>
@@ -9923,7 +9928,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9931,10 +9936,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9957,16 +9962,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10016,7 +10021,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -10031,7 +10036,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
@@ -10040,7 +10045,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -10048,13 +10053,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>79</v>
@@ -10076,17 +10081,17 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -10135,7 +10140,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -10150,16 +10155,16 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -10167,10 +10172,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10282,10 +10287,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10399,10 +10404,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10428,16 +10433,16 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10462,31 +10467,31 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y60" t="s" s="2">
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -10501,7 +10506,7 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>79</v>
@@ -10518,10 +10523,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10547,16 +10552,16 @@
         <v>266</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10584,28 +10589,28 @@
         <v>145</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -10620,7 +10625,7 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>79</v>
@@ -10629,7 +10634,7 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10637,10 +10642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10666,29 +10671,29 @@
         <v>129</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>79</v>
@@ -10724,7 +10729,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -10739,7 +10744,7 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>79</v>
@@ -10748,7 +10753,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10756,14 +10761,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10785,13 +10790,13 @@
         <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10805,7 +10810,7 @@
         <v>79</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>79</v>
@@ -10841,7 +10846,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -10856,7 +10861,7 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>79</v>
@@ -10865,7 +10870,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10873,10 +10878,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10899,13 +10904,13 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10956,7 +10961,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -10971,7 +10976,7 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>79</v>
@@ -10980,7 +10985,7 @@
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -10988,10 +10993,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11014,16 +11019,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -11073,7 +11078,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -11088,7 +11093,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>79</v>
@@ -11097,7 +11102,7 @@
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -11105,13 +11110,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>79</v>
@@ -11133,17 +11138,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -11192,7 +11197,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -11207,16 +11212,16 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -11224,10 +11229,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11339,10 +11344,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11456,10 +11461,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11485,16 +11490,16 @@
         <v>175</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -11519,31 +11524,31 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -11558,7 +11563,7 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>79</v>
@@ -11575,10 +11580,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11604,16 +11609,16 @@
         <v>266</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -11641,28 +11646,28 @@
         <v>145</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -11677,7 +11682,7 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>79</v>
@@ -11686,7 +11691,7 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -11694,10 +11699,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11723,29 +11728,29 @@
         <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>79</v>
@@ -11781,7 +11786,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -11796,7 +11801,7 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>79</v>
@@ -11805,7 +11810,7 @@
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11813,10 +11818,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11842,13 +11847,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11862,7 +11867,7 @@
         <v>79</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>79</v>
@@ -11898,7 +11903,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -11913,7 +11918,7 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>79</v>
@@ -11922,7 +11927,7 @@
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11930,10 +11935,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11956,13 +11961,13 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12013,7 +12018,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -12028,7 +12033,7 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>79</v>
@@ -12037,7 +12042,7 @@
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -12045,10 +12050,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12071,16 +12076,16 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12130,7 +12135,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -12145,7 +12150,7 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>79</v>
@@ -12154,7 +12159,7 @@
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -12162,13 +12167,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
@@ -12190,17 +12195,17 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -12249,7 +12254,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -12264,16 +12269,16 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -12281,10 +12286,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12396,10 +12401,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12513,10 +12518,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12542,16 +12547,16 @@
         <v>175</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12576,31 +12581,31 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -12615,7 +12620,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>79</v>
@@ -12632,10 +12637,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12661,16 +12666,16 @@
         <v>266</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -12698,28 +12703,28 @@
         <v>145</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -12734,7 +12739,7 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
@@ -12743,7 +12748,7 @@
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12751,10 +12756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12780,29 +12785,29 @@
         <v>129</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>79</v>
@@ -12838,7 +12843,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -12853,7 +12858,7 @@
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>79</v>
@@ -12862,7 +12867,7 @@
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12870,10 +12875,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12899,13 +12904,13 @@
         <v>101</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12919,7 +12924,7 @@
         <v>79</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>79</v>
@@ -12955,7 +12960,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -12970,7 +12975,7 @@
         <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>79</v>
@@ -12979,7 +12984,7 @@
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12987,10 +12992,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13013,13 +13018,13 @@
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13070,7 +13075,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -13085,7 +13090,7 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>79</v>
@@ -13094,7 +13099,7 @@
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -13102,10 +13107,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13128,16 +13133,16 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13187,7 +13192,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -13202,7 +13207,7 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>79</v>
@@ -13211,7 +13216,7 @@
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -13219,13 +13224,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>79</v>
@@ -13247,17 +13252,17 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -13306,7 +13311,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -13321,16 +13326,16 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -13338,10 +13343,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13453,10 +13458,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13570,10 +13575,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13599,16 +13604,16 @@
         <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -13633,31 +13638,31 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y87" t="s" s="2">
+      <c r="AA87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -13672,7 +13677,7 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
@@ -13689,10 +13694,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13718,16 +13723,16 @@
         <v>266</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13755,28 +13760,28 @@
         <v>145</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -13791,7 +13796,7 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>79</v>
@@ -13800,7 +13805,7 @@
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -13808,10 +13813,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13923,10 +13928,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14040,10 +14045,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14069,16 +14074,16 @@
         <v>141</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -14127,7 +14132,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -14142,7 +14147,7 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>79</v>
@@ -14151,7 +14156,7 @@
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -14159,10 +14164,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14274,10 +14279,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14391,10 +14396,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14423,7 +14428,7 @@
         <v>158</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>160</v>
@@ -14436,7 +14441,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>79</v>
@@ -14510,10 +14515,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14627,10 +14632,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14656,10 +14661,10 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
@@ -14670,7 +14675,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>79</v>
@@ -14744,10 +14749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14861,10 +14866,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14980,10 +14985,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15009,16 +15014,16 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
@@ -15067,7 +15072,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -15082,7 +15087,7 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>79</v>
@@ -15091,7 +15096,7 @@
         <v>79</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -15099,10 +15104,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15128,29 +15133,29 @@
         <v>129</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>79</v>
@@ -15186,7 +15191,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -15201,7 +15206,7 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>79</v>
@@ -15210,7 +15215,7 @@
         <v>79</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -15218,10 +15223,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15247,13 +15252,13 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15267,7 +15272,7 @@
         <v>79</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>79</v>
@@ -15303,7 +15308,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -15318,7 +15323,7 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>79</v>
@@ -15327,7 +15332,7 @@
         <v>79</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15335,10 +15340,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15361,13 +15366,13 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15418,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -15433,7 +15438,7 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>79</v>
@@ -15442,7 +15447,7 @@
         <v>79</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>79</v>
@@ -15450,10 +15455,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15476,16 +15481,16 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15535,7 +15540,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -15550,7 +15555,7 @@
         <v>99</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>79</v>
@@ -15559,7 +15564,7 @@
         <v>79</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>79</v>
@@ -15567,13 +15572,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -15595,17 +15600,17 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -15654,7 +15659,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -15669,16 +15674,16 @@
         <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL104" t="s" s="2">
+      <c r="AN104" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -15686,10 +15691,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15801,10 +15806,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15918,10 +15923,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15947,16 +15952,16 @@
         <v>175</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15981,31 +15986,31 @@
         <v>79</v>
       </c>
       <c r="X107" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Y107" t="s" s="2">
+      <c r="AA107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -16020,7 +16025,7 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>79</v>
@@ -16037,10 +16042,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16066,16 +16071,16 @@
         <v>266</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -16103,28 +16108,28 @@
         <v>145</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -16139,7 +16144,7 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>79</v>
@@ -16148,7 +16153,7 @@
         <v>79</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>79</v>
@@ -16156,10 +16161,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16185,29 +16190,29 @@
         <v>129</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O109" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>79</v>
@@ -16243,7 +16248,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -16258,7 +16263,7 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>79</v>
@@ -16267,7 +16272,7 @@
         <v>79</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>79</v>
@@ -16275,10 +16280,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16304,13 +16309,13 @@
         <v>101</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16324,7 +16329,7 @@
         <v>79</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>79</v>
@@ -16360,7 +16365,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -16375,7 +16380,7 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>79</v>
@@ -16384,7 +16389,7 @@
         <v>79</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>79</v>
@@ -16392,10 +16397,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16418,13 +16423,13 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16475,7 +16480,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -16490,7 +16495,7 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>79</v>
@@ -16499,7 +16504,7 @@
         <v>79</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>79</v>
@@ -16507,10 +16512,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16533,16 +16538,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16592,7 +16597,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -16607,7 +16612,7 @@
         <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>79</v>
@@ -16616,7 +16621,7 @@
         <v>79</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>79</v>
@@ -16624,10 +16629,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16653,23 +16658,23 @@
         <v>192</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="P113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q113" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="O113" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q113" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="R113" t="s" s="2">
         <v>79</v>
       </c>
@@ -16713,7 +16718,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -16728,13 +16733,13 @@
         <v>99</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>79</v>
@@ -16745,10 +16750,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16771,19 +16776,19 @@
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -16832,7 +16837,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -16847,16 +16852,16 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>79</v>
@@ -16864,10 +16869,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16979,10 +16984,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17094,23 +17099,23 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="D117" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="D117" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>79</v>
@@ -17122,13 +17127,13 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17211,10 +17216,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17240,16 +17245,16 @@
         <v>175</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -17274,31 +17279,31 @@
         <v>79</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y118" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z118" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="Z118" t="s" s="2">
+      <c r="AA118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -17313,16 +17318,16 @@
         <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>79</v>
@@ -17330,10 +17335,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17359,16 +17364,16 @@
         <v>101</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17417,7 +17422,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -17432,16 +17437,16 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17449,14 +17454,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17478,13 +17483,13 @@
         <v>101</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17534,7 +17539,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -17549,16 +17554,16 @@
         <v>99</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17566,14 +17571,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17595,13 +17600,13 @@
         <v>101</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17651,7 +17656,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -17666,16 +17671,16 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17683,10 +17688,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17712,10 +17717,10 @@
         <v>101</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17766,7 +17771,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -17781,16 +17786,16 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17798,10 +17803,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17827,10 +17832,10 @@
         <v>101</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17881,7 +17886,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -17896,16 +17901,16 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17913,10 +17918,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17939,17 +17944,17 @@
         <v>88</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17998,7 +18003,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -18013,16 +18018,16 @@
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -18030,10 +18035,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18056,19 +18061,19 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -18117,7 +18122,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -18132,16 +18137,16 @@
         <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>79</v>
@@ -18149,10 +18154,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18264,10 +18269,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18381,13 +18386,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C128" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>79</v>
@@ -18409,13 +18414,13 @@
         <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -18498,13 +18503,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>79</v>
@@ -18526,13 +18531,13 @@
         <v>79</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18615,13 +18620,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C130" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>79</v>
@@ -18643,13 +18648,13 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18732,10 +18737,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18761,10 +18766,10 @@
         <v>175</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18791,55 +18796,55 @@
         <v>79</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y131" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z131" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z131" t="s" s="2">
+      <c r="AA131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AA131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF131" t="s" s="2">
+      <c r="AG131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI131" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18847,10 +18852,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18876,16 +18881,16 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -18934,7 +18939,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -18949,16 +18954,16 @@
         <v>99</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18966,10 +18971,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18995,16 +19000,16 @@
         <v>175</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -19029,31 +19034,31 @@
         <v>79</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="Z133" t="s" s="2">
+      <c r="AA133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF133" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -19068,7 +19073,7 @@
         <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>79</v>
@@ -19077,7 +19082,7 @@
         <v>79</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -19085,10 +19090,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19111,16 +19116,16 @@
         <v>88</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -19170,7 +19175,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -19202,10 +19207,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19228,13 +19233,13 @@
         <v>88</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19285,7 +19290,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -19300,7 +19305,7 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>79</v>
@@ -19317,10 +19322,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19346,16 +19351,16 @@
         <v>175</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19380,14 +19385,14 @@
         <v>79</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y136" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="Z136" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="Z136" t="s" s="2">
-        <v>634</v>
-      </c>
       <c r="AA136" t="s" s="2">
         <v>79</v>
       </c>
@@ -19404,7 +19409,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
@@ -19419,16 +19424,16 @@
         <v>99</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL136" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AL136" t="s" s="2">
+      <c r="AM136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN136" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19436,10 +19441,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19462,19 +19467,19 @@
         <v>88</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19523,7 +19528,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>77</v>
@@ -19538,27 +19543,27 @@
         <v>99</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AL137" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AL137" t="s" s="2">
+      <c r="AM137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN137" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AM137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN137" t="s" s="2">
+      <c r="AO137" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19581,19 +19586,19 @@
         <v>88</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>79</v>
@@ -19642,7 +19647,7 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
@@ -19657,7 +19662,7 @@
         <v>99</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>105</v>
@@ -19666,7 +19671,7 @@
         <v>79</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>79</v>
@@ -19674,10 +19679,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19700,19 +19705,19 @@
         <v>88</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
@@ -19761,7 +19766,7 @@
         <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>77</v>
@@ -19776,16 +19781,16 @@
         <v>99</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AL139" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="AL139" t="s" s="2">
+      <c r="AM139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN139" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>79</v>
@@ -19793,10 +19798,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19908,10 +19913,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20023,23 +20028,23 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C142" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="B142" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C142" t="s" s="2">
+      <c r="D142" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="D142" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>79</v>
@@ -20051,13 +20056,13 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L142" t="s" s="2">
-        <v>238</v>
-      </c>
       <c r="M142" t="s" s="2">
-        <v>239</v>
+        <v>671</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -20140,16 +20145,16 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>79</v>
+        <v>674</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -20168,13 +20173,13 @@
         <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -20257,13 +20262,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>79</v>
@@ -20285,13 +20290,13 @@
         <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20374,13 +20379,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>79</v>
@@ -20402,13 +20407,13 @@
         <v>79</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20491,13 +20496,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>79</v>
@@ -20519,7 +20524,7 @@
         <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L146" t="s" s="2">
         <v>238</v>
@@ -20608,10 +20613,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20637,16 +20642,16 @@
         <v>175</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20659,7 +20664,7 @@
         <v>79</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>79</v>
@@ -20671,13 +20676,13 @@
         <v>79</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>79</v>
@@ -20695,7 +20700,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -20710,7 +20715,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>79</v>
@@ -20719,7 +20724,7 @@
         <v>79</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20727,10 +20732,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20756,13 +20761,13 @@
         <v>175</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20776,7 +20781,7 @@
         <v>79</v>
       </c>
       <c r="T148" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="U148" t="s" s="2">
         <v>79</v>
@@ -20788,13 +20793,13 @@
         <v>79</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>79</v>
@@ -20812,7 +20817,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -20827,7 +20832,7 @@
         <v>99</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>79</v>
@@ -20836,7 +20841,7 @@
         <v>79</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20844,10 +20849,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20873,16 +20878,16 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20895,7 +20900,7 @@
         <v>79</v>
       </c>
       <c r="T149" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="U149" t="s" s="2">
         <v>79</v>
@@ -20931,7 +20936,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
@@ -20946,7 +20951,7 @@
         <v>99</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>79</v>
@@ -20955,7 +20960,7 @@
         <v>79</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>79</v>
@@ -20963,10 +20968,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20992,10 +20997,10 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -21010,7 +21015,7 @@
         <v>79</v>
       </c>
       <c r="T150" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="U150" t="s" s="2">
         <v>79</v>
@@ -21046,7 +21051,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>77</v>
@@ -21061,7 +21066,7 @@
         <v>99</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>79</v>
@@ -21070,7 +21075,7 @@
         <v>79</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>79</v>
@@ -21078,14 +21083,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -21107,10 +21112,10 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -21125,7 +21130,7 @@
         <v>79</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>79</v>
@@ -21161,7 +21166,7 @@
         <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -21176,7 +21181,7 @@
         <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>79</v>
@@ -21185,7 +21190,7 @@
         <v>79</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>79</v>
@@ -21193,14 +21198,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -21222,13 +21227,13 @@
         <v>101</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21242,7 +21247,7 @@
         <v>79</v>
       </c>
       <c r="T152" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="U152" t="s" s="2">
         <v>79</v>
@@ -21278,7 +21283,7 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -21293,7 +21298,7 @@
         <v>99</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>79</v>
@@ -21302,7 +21307,7 @@
         <v>79</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>79</v>
@@ -21310,10 +21315,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21339,10 +21344,10 @@
         <v>101</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21425,10 +21430,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21538,13 +21543,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
@@ -21566,13 +21571,13 @@
         <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21632,13 +21637,13 @@
         <v>78</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>79</v>
@@ -21655,13 +21660,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>79</v>
@@ -21683,13 +21688,13 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21772,10 +21777,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21801,10 +21806,10 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21828,7 +21833,7 @@
         <v>79</v>
       </c>
       <c r="W157" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="X157" t="s" s="2">
         <v>79</v>
@@ -21855,7 +21860,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>77</v>
@@ -21887,14 +21892,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21916,10 +21921,10 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21970,7 +21975,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>77</v>
@@ -21985,7 +21990,7 @@
         <v>99</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>79</v>
@@ -21994,7 +21999,7 @@
         <v>79</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -22002,14 +22007,14 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22031,10 +22036,10 @@
         <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -22049,7 +22054,7 @@
         <v>79</v>
       </c>
       <c r="T159" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="U159" t="s" s="2">
         <v>79</v>
@@ -22085,7 +22090,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>77</v>
@@ -22100,7 +22105,7 @@
         <v>99</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
@@ -22109,7 +22114,7 @@
         <v>79</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>79</v>
@@ -22117,10 +22122,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22146,13 +22151,13 @@
         <v>101</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -22202,7 +22207,7 @@
         <v>79</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>77</v>
@@ -22217,7 +22222,7 @@
         <v>99</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>79</v>
@@ -22226,7 +22231,7 @@
         <v>79</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>79</v>
@@ -22234,10 +22239,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22260,17 +22265,17 @@
         <v>88</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>79</v>
@@ -22283,7 +22288,7 @@
         <v>79</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>79</v>
@@ -22319,7 +22324,7 @@
         <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
@@ -22334,7 +22339,7 @@
         <v>99</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>79</v>
@@ -22343,7 +22348,7 @@
         <v>79</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>79</v>
@@ -22351,10 +22356,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22466,10 +22471,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22583,10 +22588,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22609,16 +22614,16 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22668,7 +22673,7 @@
         <v>79</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>77</v>
@@ -22677,13 +22682,13 @@
         <v>87</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>79</v>
@@ -22692,7 +22697,7 @@
         <v>79</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>79</v>
@@ -22700,10 +22705,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22726,23 +22731,23 @@
         <v>88</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q165" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="R165" t="s" s="2">
         <v>79</v>
@@ -22787,7 +22792,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -22796,13 +22801,13 @@
         <v>87</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>79</v>
@@ -22811,7 +22816,7 @@
         <v>79</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>79</v>
@@ -22819,10 +22824,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22848,14 +22853,14 @@
         <v>266</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>79</v>
@@ -22883,10 +22888,10 @@
         <v>145</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22904,7 +22909,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -22919,16 +22924,16 @@
         <v>99</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>79</v>
@@ -22936,10 +22941,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22962,19 +22967,19 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -23023,7 +23028,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>77</v>
@@ -23038,7 +23043,7 @@
         <v>99</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>105</v>
@@ -23047,7 +23052,7 @@
         <v>79</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23055,10 +23060,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23081,19 +23086,19 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23142,7 +23147,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>77</v>
@@ -23157,7 +23162,7 @@
         <v>99</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>105</v>
@@ -23166,7 +23171,7 @@
         <v>79</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23174,10 +23179,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23200,19 +23205,19 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23261,7 +23266,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>77</v>
@@ -23273,10 +23278,10 @@
         <v>79</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>105</v>
@@ -23293,10 +23298,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23408,10 +23413,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23521,13 +23526,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23549,13 +23554,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23615,7 +23620,7 @@
         <v>78</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>116</v>
@@ -23638,13 +23643,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>79</v>
@@ -23666,13 +23671,13 @@
         <v>79</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23732,7 +23737,7 @@
         <v>78</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>116</v>
@@ -23755,14 +23760,14 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -23784,16 +23789,16 @@
         <v>108</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>79</v>
@@ -23842,7 +23847,7 @@
         <v>79</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>77</v>
@@ -23874,10 +23879,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23903,14 +23908,14 @@
         <v>266</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>79</v>
@@ -23938,10 +23943,10 @@
         <v>145</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>79</v>
@@ -23959,7 +23964,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>77</v>
@@ -23983,7 +23988,7 @@
         <v>79</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>79</v>
@@ -23991,10 +23996,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24106,10 +24111,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24223,10 +24228,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24252,16 +24257,16 @@
         <v>141</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24308,7 +24313,7 @@
         <v>114</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>77</v>
@@ -24323,7 +24328,7 @@
         <v>99</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>79</v>
@@ -24332,7 +24337,7 @@
         <v>79</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24340,13 +24345,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>79</v>
@@ -24371,16 +24376,16 @@
         <v>141</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24429,7 +24434,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>77</v>
@@ -24444,7 +24449,7 @@
         <v>99</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>79</v>
@@ -24453,7 +24458,7 @@
         <v>79</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>79</v>
@@ -24461,10 +24466,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24576,10 +24581,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24693,10 +24698,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24738,7 +24743,7 @@
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>79</v>
@@ -24812,10 +24817,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24929,10 +24934,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24958,10 +24963,10 @@
         <v>175</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
@@ -25046,10 +25051,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25163,10 +25168,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25282,10 +25287,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25311,16 +25316,16 @@
         <v>101</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25369,7 +25374,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>77</v>
@@ -25384,7 +25389,7 @@
         <v>99</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>79</v>
@@ -25393,7 +25398,7 @@
         <v>79</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25401,10 +25406,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25427,17 +25432,17 @@
         <v>79</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25486,7 +25491,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>77</v>
@@ -25501,7 +25506,7 @@
         <v>99</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>105</v>
@@ -25510,7 +25515,7 @@
         <v>79</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25518,10 +25523,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25544,19 +25549,19 @@
         <v>79</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -25605,7 +25610,7 @@
         <v>79</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>77</v>
@@ -25620,7 +25625,7 @@
         <v>99</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>105</v>
@@ -25629,7 +25634,7 @@
         <v>79</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>79</v>
@@ -25637,10 +25642,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25663,17 +25668,17 @@
         <v>79</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>79</v>
@@ -25722,7 +25727,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>77</v>
@@ -25737,7 +25742,7 @@
         <v>99</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>105</v>
@@ -25746,7 +25751,7 @@
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25754,10 +25759,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25783,14 +25788,14 @@
         <v>175</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -25815,14 +25820,14 @@
         <v>79</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y191" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="Z191" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="Z191" t="s" s="2">
-        <v>634</v>
-      </c>
       <c r="AA191" t="s" s="2">
         <v>79</v>
       </c>
@@ -25839,7 +25844,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>77</v>
@@ -25854,7 +25859,7 @@
         <v>99</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>105</v>
@@ -25863,7 +25868,7 @@
         <v>79</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>79</v>
@@ -25871,10 +25876,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25897,17 +25902,17 @@
         <v>79</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>79</v>
@@ -25956,7 +25961,7 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -25965,13 +25970,13 @@
         <v>87</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="AL192" t="s" s="2">
         <v>105</v>
@@ -25980,7 +25985,7 @@
         <v>79</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>79</v>
@@ -25988,10 +25993,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26014,13 +26019,13 @@
         <v>79</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -26071,7 +26076,7 @@
         <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>77</v>
@@ -26086,7 +26091,7 @@
         <v>99</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>105</v>
@@ -26103,10 +26108,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26129,19 +26134,19 @@
         <v>79</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>79</v>
@@ -26190,7 +26195,7 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>77</v>
@@ -26205,10 +26210,10 @@
         <v>99</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>79</v>
@@ -26222,10 +26227,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26337,10 +26342,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26454,14 +26459,14 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
@@ -26483,16 +26488,16 @@
         <v>108</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N197" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>79</v>
@@ -26541,7 +26546,7 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>77</v>
@@ -26573,10 +26578,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26602,16 +26607,16 @@
         <v>266</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>79</v>
@@ -26660,7 +26665,7 @@
         <v>79</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>87</v>
@@ -26675,16 +26680,16 @@
         <v>99</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>79</v>
@@ -26692,10 +26697,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26807,10 +26812,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26924,10 +26929,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26953,16 +26958,16 @@
         <v>141</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M201" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M201" t="s" s="2">
+      <c r="O201" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>79</v>
@@ -27009,7 +27014,7 @@
         <v>114</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>77</v>
@@ -27024,7 +27029,7 @@
         <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>79</v>
@@ -27033,7 +27038,7 @@
         <v>79</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>79</v>
@@ -27041,13 +27046,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>79</v>
@@ -27072,16 +27077,16 @@
         <v>141</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M202" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M202" t="s" s="2">
+      <c r="O202" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>79</v>
@@ -27130,7 +27135,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>77</v>
@@ -27145,7 +27150,7 @@
         <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>79</v>
@@ -27154,7 +27159,7 @@
         <v>79</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>79</v>
@@ -27162,10 +27167,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27277,10 +27282,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27394,13 +27399,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
@@ -27422,13 +27427,13 @@
         <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -27511,10 +27516,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27626,10 +27631,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27741,10 +27746,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27784,7 +27789,7 @@
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="S208" t="s" s="2">
         <v>79</v>
@@ -27858,10 +27863,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27884,13 +27889,13 @@
         <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>946</v>
+        <v>284</v>
       </c>
       <c r="L209" t="s" s="2">
         <v>267</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27929,17 +27934,17 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AC209" s="2"/>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -27971,13 +27976,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D210" t="s" s="2">
         <v>79</v>
@@ -28005,7 +28010,7 @@
         <v>267</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -28056,7 +28061,7 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -28088,10 +28093,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28133,7 +28138,7 @@
       </c>
       <c r="Q211" s="2"/>
       <c r="R211" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="S211" t="s" s="2">
         <v>79</v>
@@ -28207,10 +28212,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28324,10 +28329,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28353,10 +28358,10 @@
         <v>175</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
@@ -28441,10 +28446,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28558,10 +28563,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28677,13 +28682,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D216" t="s" s="2">
         <v>79</v>
@@ -28708,16 +28713,16 @@
         <v>141</v>
       </c>
       <c r="L216" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M216" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N216" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M216" t="s" s="2">
+      <c r="O216" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N216" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
@@ -28742,11 +28747,11 @@
         <v>79</v>
       </c>
       <c r="X216" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>79</v>
@@ -28764,7 +28769,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>77</v>
@@ -28779,7 +28784,7 @@
         <v>99</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>79</v>
@@ -28788,7 +28793,7 @@
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>79</v>
@@ -28796,10 +28801,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28911,10 +28916,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29028,10 +29033,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29147,10 +29152,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29264,10 +29269,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29293,10 +29298,10 @@
         <v>175</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" t="s" s="2">
@@ -29381,10 +29386,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29498,10 +29503,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29617,10 +29622,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29646,16 +29651,16 @@
         <v>101</v>
       </c>
       <c r="L224" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M224" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N224" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M224" t="s" s="2">
+      <c r="O224" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O224" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>79</v>
@@ -29704,7 +29709,7 @@
         <v>79</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>77</v>
@@ -29719,7 +29724,7 @@
         <v>99</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>79</v>
@@ -29728,7 +29733,7 @@
         <v>79</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>79</v>
@@ -29736,10 +29741,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29765,16 +29770,16 @@
         <v>192</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>79</v>
@@ -29823,7 +29828,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>77</v>
@@ -29838,16 +29843,16 @@
         <v>99</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>79</v>
@@ -29855,14 +29860,14 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
@@ -29881,16 +29886,16 @@
         <v>79</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -29940,7 +29945,7 @@
         <v>79</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>77</v>
@@ -29955,7 +29960,7 @@
         <v>99</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AL226" t="s" s="2">
         <v>105</v>
@@ -29964,7 +29969,7 @@
         <v>79</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>79</v>
@@ -29972,10 +29977,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29998,19 +30003,19 @@
         <v>88</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>79</v>
@@ -30059,7 +30064,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>77</v>
@@ -30074,10 +30079,10 @@
         <v>99</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>79</v>
@@ -30091,10 +30096,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30117,19 +30122,19 @@
         <v>88</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>79</v>
@@ -30178,7 +30183,7 @@
         <v>79</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>77</v>
@@ -30193,7 +30198,7 @@
         <v>99</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AL228" t="s" s="2">
         <v>105</v>
@@ -30210,10 +30215,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30325,10 +30330,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30442,14 +30447,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
@@ -30471,16 +30476,16 @@
         <v>108</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="N231" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>79</v>
@@ -30529,7 +30534,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>77</v>
@@ -30561,10 +30566,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30587,16 +30592,16 @@
         <v>88</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -30646,7 +30651,7 @@
         <v>79</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>87</v>
@@ -30661,7 +30666,7 @@
         <v>99</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AL232" t="s" s="2">
         <v>105</v>
@@ -30670,7 +30675,7 @@
         <v>79</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AO232" t="s" s="2">
         <v>79</v>
@@ -30678,10 +30683,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30707,10 +30712,10 @@
         <v>175</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -30737,13 +30742,13 @@
         <v>79</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>79</v>
@@ -30761,7 +30766,7 @@
         <v>79</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>87</v>
@@ -30776,7 +30781,7 @@
         <v>99</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>105</v>

--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T19:39:02+00:00</t>
+    <t>2026-09-18T19:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T19:41:15+00:00</t>
+    <t>2026-09-29T03:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DIPSPatient.xlsx
+++ b/docs/StructureDefinition-DIPSPatient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T03:57:01+00:00</t>
+    <t>2026-09-29T04:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
